--- a/www/flightdata/xlsx/eoss-298.xlsx
+++ b/www/flightdata/xlsx/eoss-298.xlsx
@@ -3531,7 +3531,7 @@
         <v>25712.32</v>
       </c>
       <c r="I2">
-        <v>651</v>
+        <v>452</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
